--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/InvestorMerger001.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/InvestorMerger001.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\code\huaxia\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="2715" windowWidth="13110" windowHeight="2520"/>
   </bookViews>
@@ -15,75 +20,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="332">
-  <si>
-    <t>登记银行代码*</t>
-  </si>
-  <si>
-    <t>识别标识*</t>
-  </si>
-  <si>
-    <t>原识别标识</t>
-  </si>
-  <si>
-    <t>该投资者是否属于本行</t>
-  </si>
-  <si>
-    <t>投资者所属银行名称</t>
-  </si>
-  <si>
-    <t>投资者所属银行代码</t>
-  </si>
-  <si>
-    <t>投资者境内外标识</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="335">
   <si>
     <t>投资者所属国家或地区</t>
   </si>
   <si>
-    <t>投资者类别*</t>
-  </si>
-  <si>
     <t>个人证件类别</t>
   </si>
   <si>
     <t>机构证件类别</t>
-  </si>
-  <si>
-    <t>其他证件名称</t>
-  </si>
-  <si>
-    <t>证件号码*</t>
-  </si>
-  <si>
-    <t>SPV资金托管账户开户行</t>
-  </si>
-  <si>
-    <t>其他资金托管账户开户行</t>
-  </si>
-  <si>
-    <t>投资者名称*</t>
-  </si>
-  <si>
-    <t>性别*</t>
-  </si>
-  <si>
-    <t>风险偏好*</t>
-  </si>
-  <si>
-    <t>手机号码</t>
-  </si>
-  <si>
-    <t>固定电话</t>
-  </si>
-  <si>
-    <t>电子邮箱</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>经办人</t>
   </si>
   <si>
     <r>
@@ -1046,11 +991,103 @@
     <t>ZWE 津巴布韦</t>
   </si>
   <si>
-    <t>接入检查结果</t>
+    <t>合并状态</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
-    <t>中债反馈消息</t>
+    <t>数据日期</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>合并后识别标识选择</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>合并人</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>合并时间</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>识别标识</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>合并后识别标识</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>投资者所属国家或地区</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>该投资者是否属于本行</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>投资者名称</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>证件号码</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>原识别标识</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>投资者所属银行名称</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>投资者所属银行代码</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>投资者境内外标识</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>投资者类别</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>其他证件名称</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>SPV资金托管账户及开户行</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>其他资金托管账户及开户行</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>性别</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>风险偏好</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>手机号码</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>固定电话</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>电子邮箱</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
 </sst>
@@ -1266,7 +1303,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1297,9 +1334,6 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -1313,6 +1347,27 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1321,74 +1376,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1401,14 +1388,14 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="CCE8CF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -1443,7 +1430,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1478,7 +1465,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1690,9 +1677,9 @@
   <dimension ref="A1:AA34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="14.875" style="10" customWidth="1"/>
-    <col min="2" max="2" width="20.75" style="10" customWidth="1"/>
-    <col min="3" max="3" width="20.5" style="10" customWidth="1"/>
+    <col min="1" max="1" width="14.875" style="28" customWidth="1"/>
+    <col min="2" max="2" width="20.75" style="28" customWidth="1"/>
+    <col min="3" max="3" width="20.5" style="28" customWidth="1"/>
     <col min="4" max="4" width="23.25" style="10" customWidth="1"/>
     <col min="5" max="5" width="27.625" style="10" customWidth="1"/>
     <col min="6" max="6" width="19.625" style="10" customWidth="1"/>
@@ -1706,99 +1693,103 @@
     <col min="14" max="14" width="23.25" style="10" customWidth="1"/>
     <col min="15" max="15" width="23.375" style="10" customWidth="1"/>
     <col min="16" max="16" width="23.25" style="10" customWidth="1"/>
-    <col min="17" max="17" width="8.875" style="10" customWidth="1"/>
-    <col min="18" max="18" width="10.875" style="10" customWidth="1"/>
-    <col min="19" max="19" width="12.75" style="10" customWidth="1"/>
-    <col min="20" max="20" width="13.25" style="10" customWidth="1"/>
-    <col min="21" max="21" width="16.375" style="10" customWidth="1"/>
+    <col min="17" max="17" width="25.25" style="10" customWidth="1"/>
+    <col min="18" max="18" width="13.875" style="10" customWidth="1"/>
+    <col min="19" max="19" width="15" style="10" customWidth="1"/>
+    <col min="20" max="20" width="28" style="10" customWidth="1"/>
+    <col min="21" max="21" width="31.625" style="10" customWidth="1"/>
     <col min="22" max="22" width="12.5" style="11" customWidth="1"/>
     <col min="23" max="24" width="18.25" style="11" customWidth="1"/>
-    <col min="25" max="25" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="25" max="27" width="14.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="21" customHeight="1">
-      <c r="A1" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="12" t="s">
+      <c r="A1" s="23" t="s">
+        <v>310</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>311</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>312</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="J1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="K1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="12" t="s">
-        <v>10</v>
-      </c>
       <c r="L1" s="12" t="s">
-        <v>11</v>
+        <v>320</v>
       </c>
       <c r="M1" s="12" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="N1" s="12" t="s">
-        <v>13</v>
+        <v>322</v>
       </c>
       <c r="O1" s="12" t="s">
-        <v>14</v>
+        <v>323</v>
       </c>
       <c r="P1" s="12" t="s">
-        <v>15</v>
+        <v>324</v>
       </c>
       <c r="Q1" s="12" t="s">
-        <v>16</v>
+        <v>317</v>
       </c>
       <c r="R1" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="18" t="s">
-        <v>20</v>
+        <v>325</v>
+      </c>
+      <c r="S1" s="17" t="s">
+        <v>326</v>
+      </c>
+      <c r="T1" s="17" t="s">
+        <v>327</v>
+      </c>
+      <c r="U1" s="17" t="s">
+        <v>328</v>
       </c>
       <c r="V1" s="12" t="s">
-        <v>21</v>
+        <v>329</v>
       </c>
       <c r="W1" s="12" t="s">
-        <v>22</v>
+        <v>330</v>
       </c>
       <c r="X1" s="12" t="s">
-        <v>330</v>
-      </c>
-      <c r="Y1" s="22" t="s">
         <v>331</v>
       </c>
-      <c r="Z1" s="6"/>
-      <c r="AA1" s="6"/>
+      <c r="Y1" s="21" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z1" s="21" t="s">
+        <v>333</v>
+      </c>
+      <c r="AA1" s="21" t="s">
+        <v>334</v>
+      </c>
     </row>
     <row r="2" spans="1:27">
-      <c r="A2" s="13"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
+      <c r="A2" s="24"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
       <c r="D2" s="13"/>
       <c r="E2" s="15"/>
       <c r="F2" s="13"/>
@@ -1814,20 +1805,20 @@
       <c r="P2" s="13"/>
       <c r="Q2" s="13"/>
       <c r="R2" s="13"/>
-      <c r="S2" s="19"/>
-      <c r="T2" s="19"/>
-      <c r="U2" s="20"/>
+      <c r="S2" s="18"/>
+      <c r="T2" s="18"/>
+      <c r="U2" s="19"/>
       <c r="V2" s="13"/>
       <c r="W2" s="13"/>
       <c r="X2" s="13"/>
-      <c r="Y2" s="23"/>
-      <c r="Z2" s="6"/>
-      <c r="AA2" s="6"/>
+      <c r="Y2" s="22"/>
+      <c r="Z2" s="22"/>
+      <c r="AA2" s="22"/>
     </row>
     <row r="3" spans="1:27">
-      <c r="A3" s="13"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
+      <c r="A3" s="24"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
       <c r="D3" s="13"/>
       <c r="E3" s="13"/>
       <c r="F3" s="13"/>
@@ -1843,20 +1834,20 @@
       <c r="P3" s="13"/>
       <c r="Q3" s="13"/>
       <c r="R3" s="13"/>
-      <c r="S3" s="21"/>
-      <c r="T3" s="21"/>
-      <c r="U3" s="21"/>
+      <c r="S3" s="20"/>
+      <c r="T3" s="20"/>
+      <c r="U3" s="20"/>
       <c r="V3" s="13"/>
       <c r="W3" s="13"/>
       <c r="X3" s="13"/>
-      <c r="Y3" s="23"/>
-      <c r="Z3" s="6"/>
-      <c r="AA3" s="6"/>
+      <c r="Y3" s="22"/>
+      <c r="Z3" s="22"/>
+      <c r="AA3" s="22"/>
     </row>
     <row r="4" spans="1:27">
-      <c r="A4" s="13"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
+      <c r="A4" s="24"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
@@ -1872,20 +1863,20 @@
       <c r="P4" s="13"/>
       <c r="Q4" s="13"/>
       <c r="R4" s="13"/>
-      <c r="S4" s="21"/>
-      <c r="T4" s="21"/>
-      <c r="U4" s="21"/>
+      <c r="S4" s="20"/>
+      <c r="T4" s="20"/>
+      <c r="U4" s="20"/>
       <c r="V4" s="13"/>
       <c r="W4" s="13"/>
       <c r="X4" s="13"/>
-      <c r="Y4" s="23"/>
-      <c r="Z4" s="6"/>
-      <c r="AA4" s="6"/>
+      <c r="Y4" s="22"/>
+      <c r="Z4" s="22"/>
+      <c r="AA4" s="22"/>
     </row>
     <row r="5" spans="1:27">
-      <c r="A5" s="13"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
+      <c r="A5" s="24"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
@@ -1901,21 +1892,21 @@
       <c r="P5" s="13"/>
       <c r="Q5" s="13"/>
       <c r="R5" s="13"/>
-      <c r="S5" s="21"/>
-      <c r="T5" s="21"/>
-      <c r="U5" s="21"/>
+      <c r="S5" s="20"/>
+      <c r="T5" s="20"/>
+      <c r="U5" s="20"/>
       <c r="V5" s="13"/>
       <c r="W5" s="13"/>
       <c r="X5" s="13"/>
-      <c r="Y5" s="23"/>
-      <c r="Z5" s="6"/>
-      <c r="AA5" s="6"/>
+      <c r="Y5" s="22"/>
+      <c r="Z5" s="22"/>
+      <c r="AA5" s="22"/>
     </row>
     <row r="6" spans="1:27">
-      <c r="A6" s="16"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
+      <c r="A6" s="26"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="16"/>
       <c r="E6" s="13"/>
       <c r="F6" s="13"/>
       <c r="G6" s="13"/>
@@ -1930,20 +1921,20 @@
       <c r="P6" s="13"/>
       <c r="Q6" s="13"/>
       <c r="R6" s="13"/>
-      <c r="S6" s="21"/>
-      <c r="T6" s="21"/>
-      <c r="U6" s="21"/>
+      <c r="S6" s="20"/>
+      <c r="T6" s="20"/>
+      <c r="U6" s="20"/>
       <c r="V6" s="13"/>
       <c r="W6" s="13"/>
       <c r="X6" s="13"/>
-      <c r="Y6" s="23"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="6"/>
+      <c r="Y6" s="22"/>
+      <c r="Z6" s="22"/>
+      <c r="AA6" s="22"/>
     </row>
     <row r="7" spans="1:27">
-      <c r="A7" s="13"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
+      <c r="A7" s="24"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="24"/>
       <c r="D7" s="13"/>
       <c r="E7" s="13"/>
       <c r="F7" s="13"/>
@@ -1959,20 +1950,20 @@
       <c r="P7" s="13"/>
       <c r="Q7" s="13"/>
       <c r="R7" s="13"/>
-      <c r="S7" s="21"/>
-      <c r="T7" s="21"/>
-      <c r="U7" s="21"/>
+      <c r="S7" s="20"/>
+      <c r="T7" s="20"/>
+      <c r="U7" s="20"/>
       <c r="V7" s="13"/>
       <c r="W7" s="13"/>
       <c r="X7" s="13"/>
-      <c r="Y7" s="23"/>
-      <c r="Z7" s="6"/>
-      <c r="AA7" s="6"/>
+      <c r="Y7" s="22"/>
+      <c r="Z7" s="22"/>
+      <c r="AA7" s="22"/>
     </row>
     <row r="8" spans="1:27">
-      <c r="A8" s="13"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
+      <c r="A8" s="24"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="24"/>
       <c r="D8" s="13"/>
       <c r="E8" s="13"/>
       <c r="F8" s="13"/>
@@ -1988,20 +1979,20 @@
       <c r="P8" s="13"/>
       <c r="Q8" s="13"/>
       <c r="R8" s="13"/>
-      <c r="S8" s="21"/>
-      <c r="T8" s="21"/>
-      <c r="U8" s="21"/>
+      <c r="S8" s="20"/>
+      <c r="T8" s="20"/>
+      <c r="U8" s="20"/>
       <c r="V8" s="13"/>
       <c r="W8" s="13"/>
       <c r="X8" s="13"/>
-      <c r="Y8" s="23"/>
-      <c r="Z8" s="6"/>
-      <c r="AA8" s="6"/>
+      <c r="Y8" s="22"/>
+      <c r="Z8" s="22"/>
+      <c r="AA8" s="22"/>
     </row>
     <row r="9" spans="1:27">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
+      <c r="A9" s="24"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
       <c r="D9" s="13"/>
       <c r="E9" s="13"/>
       <c r="F9" s="13"/>
@@ -2017,20 +2008,20 @@
       <c r="P9" s="13"/>
       <c r="Q9" s="13"/>
       <c r="R9" s="13"/>
-      <c r="S9" s="21"/>
-      <c r="T9" s="21"/>
-      <c r="U9" s="21"/>
+      <c r="S9" s="20"/>
+      <c r="T9" s="20"/>
+      <c r="U9" s="20"/>
       <c r="V9" s="13"/>
       <c r="W9" s="13"/>
       <c r="X9" s="13"/>
-      <c r="Y9" s="23"/>
-      <c r="Z9" s="6"/>
-      <c r="AA9" s="6"/>
+      <c r="Y9" s="22"/>
+      <c r="Z9" s="22"/>
+      <c r="AA9" s="22"/>
     </row>
     <row r="10" spans="1:27">
-      <c r="A10" s="13"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
+      <c r="A10" s="24"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
       <c r="D10" s="13"/>
       <c r="E10" s="13"/>
       <c r="F10" s="13"/>
@@ -2046,20 +2037,20 @@
       <c r="P10" s="13"/>
       <c r="Q10" s="13"/>
       <c r="R10" s="13"/>
-      <c r="S10" s="21"/>
-      <c r="T10" s="21"/>
-      <c r="U10" s="21"/>
+      <c r="S10" s="20"/>
+      <c r="T10" s="20"/>
+      <c r="U10" s="20"/>
       <c r="V10" s="13"/>
       <c r="W10" s="13"/>
       <c r="X10" s="13"/>
-      <c r="Y10" s="23"/>
-      <c r="Z10" s="6"/>
-      <c r="AA10" s="6"/>
+      <c r="Y10" s="22"/>
+      <c r="Z10" s="22"/>
+      <c r="AA10" s="22"/>
     </row>
     <row r="11" spans="1:27">
-      <c r="A11" s="13"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
+      <c r="A11" s="24"/>
+      <c r="B11" s="24"/>
+      <c r="C11" s="24"/>
       <c r="D11" s="13"/>
       <c r="E11" s="13"/>
       <c r="F11" s="13"/>
@@ -2075,20 +2066,20 @@
       <c r="P11" s="13"/>
       <c r="Q11" s="13"/>
       <c r="R11" s="13"/>
-      <c r="S11" s="21"/>
-      <c r="T11" s="21"/>
-      <c r="U11" s="21"/>
+      <c r="S11" s="20"/>
+      <c r="T11" s="20"/>
+      <c r="U11" s="20"/>
       <c r="V11" s="13"/>
       <c r="W11" s="13"/>
       <c r="X11" s="13"/>
-      <c r="Y11" s="23"/>
-      <c r="Z11" s="6"/>
-      <c r="AA11" s="6"/>
+      <c r="Y11" s="22"/>
+      <c r="Z11" s="22"/>
+      <c r="AA11" s="22"/>
     </row>
     <row r="12" spans="1:27">
-      <c r="A12" s="13"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
+      <c r="A12" s="24"/>
+      <c r="B12" s="24"/>
+      <c r="C12" s="24"/>
       <c r="D12" s="13"/>
       <c r="E12" s="13"/>
       <c r="F12" s="13"/>
@@ -2104,20 +2095,20 @@
       <c r="P12" s="13"/>
       <c r="Q12" s="13"/>
       <c r="R12" s="13"/>
-      <c r="S12" s="21"/>
-      <c r="T12" s="21"/>
-      <c r="U12" s="21"/>
+      <c r="S12" s="20"/>
+      <c r="T12" s="20"/>
+      <c r="U12" s="20"/>
       <c r="V12" s="13"/>
       <c r="W12" s="13"/>
       <c r="X12" s="13"/>
-      <c r="Y12" s="23"/>
-      <c r="Z12" s="6"/>
-      <c r="AA12" s="6"/>
+      <c r="Y12" s="22"/>
+      <c r="Z12" s="22"/>
+      <c r="AA12" s="22"/>
     </row>
     <row r="13" spans="1:27">
-      <c r="A13" s="13"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
+      <c r="A13" s="24"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
       <c r="D13" s="13"/>
       <c r="E13" s="13"/>
       <c r="F13" s="13"/>
@@ -2133,20 +2124,20 @@
       <c r="P13" s="13"/>
       <c r="Q13" s="13"/>
       <c r="R13" s="13"/>
-      <c r="S13" s="21"/>
-      <c r="T13" s="21"/>
-      <c r="U13" s="21"/>
+      <c r="S13" s="20"/>
+      <c r="T13" s="20"/>
+      <c r="U13" s="20"/>
       <c r="V13" s="13"/>
       <c r="W13" s="13"/>
       <c r="X13" s="13"/>
-      <c r="Y13" s="23"/>
-      <c r="Z13" s="6"/>
-      <c r="AA13" s="6"/>
+      <c r="Y13" s="22"/>
+      <c r="Z13" s="22"/>
+      <c r="AA13" s="22"/>
     </row>
     <row r="14" spans="1:27">
-      <c r="A14" s="13"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
+      <c r="A14" s="24"/>
+      <c r="B14" s="24"/>
+      <c r="C14" s="24"/>
       <c r="D14" s="13"/>
       <c r="E14" s="13"/>
       <c r="F14" s="13"/>
@@ -2162,20 +2153,20 @@
       <c r="P14" s="13"/>
       <c r="Q14" s="13"/>
       <c r="R14" s="13"/>
-      <c r="S14" s="21"/>
-      <c r="T14" s="21"/>
-      <c r="U14" s="21"/>
+      <c r="S14" s="20"/>
+      <c r="T14" s="20"/>
+      <c r="U14" s="20"/>
       <c r="V14" s="13"/>
       <c r="W14" s="13"/>
       <c r="X14" s="13"/>
-      <c r="Y14" s="23"/>
-      <c r="Z14" s="6"/>
-      <c r="AA14" s="6"/>
+      <c r="Y14" s="22"/>
+      <c r="Z14" s="22"/>
+      <c r="AA14" s="22"/>
     </row>
     <row r="15" spans="1:27">
-      <c r="A15" s="13"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
+      <c r="A15" s="24"/>
+      <c r="B15" s="24"/>
+      <c r="C15" s="24"/>
       <c r="D15" s="13"/>
       <c r="E15" s="13"/>
       <c r="F15" s="13"/>
@@ -2191,20 +2182,20 @@
       <c r="P15" s="13"/>
       <c r="Q15" s="13"/>
       <c r="R15" s="13"/>
-      <c r="S15" s="21"/>
-      <c r="T15" s="21"/>
-      <c r="U15" s="21"/>
+      <c r="S15" s="20"/>
+      <c r="T15" s="20"/>
+      <c r="U15" s="20"/>
       <c r="V15" s="13"/>
       <c r="W15" s="13"/>
       <c r="X15" s="13"/>
-      <c r="Y15" s="23"/>
-      <c r="Z15" s="6"/>
-      <c r="AA15" s="6"/>
+      <c r="Y15" s="22"/>
+      <c r="Z15" s="22"/>
+      <c r="AA15" s="22"/>
     </row>
     <row r="16" spans="1:27">
-      <c r="A16" s="13"/>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
+      <c r="A16" s="24"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="24"/>
       <c r="D16" s="13"/>
       <c r="E16" s="13"/>
       <c r="F16" s="13"/>
@@ -2220,20 +2211,20 @@
       <c r="P16" s="13"/>
       <c r="Q16" s="13"/>
       <c r="R16" s="13"/>
-      <c r="S16" s="21"/>
-      <c r="T16" s="21"/>
-      <c r="U16" s="21"/>
+      <c r="S16" s="20"/>
+      <c r="T16" s="20"/>
+      <c r="U16" s="20"/>
       <c r="V16" s="13"/>
       <c r="W16" s="13"/>
       <c r="X16" s="13"/>
-      <c r="Y16" s="23"/>
-      <c r="Z16" s="6"/>
-      <c r="AA16" s="6"/>
+      <c r="Y16" s="22"/>
+      <c r="Z16" s="22"/>
+      <c r="AA16" s="22"/>
     </row>
     <row r="17" spans="1:27">
-      <c r="A17" s="13"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
+      <c r="A17" s="24"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="24"/>
       <c r="D17" s="13"/>
       <c r="E17" s="13"/>
       <c r="F17" s="13"/>
@@ -2249,20 +2240,20 @@
       <c r="P17" s="13"/>
       <c r="Q17" s="13"/>
       <c r="R17" s="13"/>
-      <c r="S17" s="21"/>
-      <c r="T17" s="21"/>
-      <c r="U17" s="21"/>
+      <c r="S17" s="20"/>
+      <c r="T17" s="20"/>
+      <c r="U17" s="20"/>
       <c r="V17" s="13"/>
       <c r="W17" s="13"/>
       <c r="X17" s="13"/>
-      <c r="Y17" s="23"/>
-      <c r="Z17" s="6"/>
-      <c r="AA17" s="6"/>
+      <c r="Y17" s="22"/>
+      <c r="Z17" s="22"/>
+      <c r="AA17" s="22"/>
     </row>
     <row r="18" spans="1:27">
-      <c r="A18" s="13"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
+      <c r="A18" s="24"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
       <c r="D18" s="13"/>
       <c r="E18" s="13"/>
       <c r="F18" s="13"/>
@@ -2278,20 +2269,20 @@
       <c r="P18" s="13"/>
       <c r="Q18" s="13"/>
       <c r="R18" s="13"/>
-      <c r="S18" s="21"/>
-      <c r="T18" s="21"/>
-      <c r="U18" s="21"/>
+      <c r="S18" s="20"/>
+      <c r="T18" s="20"/>
+      <c r="U18" s="20"/>
       <c r="V18" s="13"/>
       <c r="W18" s="13"/>
       <c r="X18" s="13"/>
-      <c r="Y18" s="23"/>
-      <c r="Z18" s="6"/>
-      <c r="AA18" s="6"/>
+      <c r="Y18" s="22"/>
+      <c r="Z18" s="22"/>
+      <c r="AA18" s="22"/>
     </row>
     <row r="19" spans="1:27">
-      <c r="A19" s="13"/>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
+      <c r="A19" s="24"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
       <c r="D19" s="13"/>
       <c r="E19" s="13"/>
       <c r="F19" s="13"/>
@@ -2307,20 +2298,20 @@
       <c r="P19" s="13"/>
       <c r="Q19" s="13"/>
       <c r="R19" s="13"/>
-      <c r="S19" s="21"/>
-      <c r="T19" s="21"/>
-      <c r="U19" s="21"/>
+      <c r="S19" s="20"/>
+      <c r="T19" s="20"/>
+      <c r="U19" s="20"/>
       <c r="V19" s="13"/>
       <c r="W19" s="13"/>
       <c r="X19" s="13"/>
-      <c r="Y19" s="23"/>
-      <c r="Z19" s="6"/>
-      <c r="AA19" s="6"/>
+      <c r="Y19" s="22"/>
+      <c r="Z19" s="22"/>
+      <c r="AA19" s="22"/>
     </row>
     <row r="20" spans="1:27">
-      <c r="A20" s="13"/>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
+      <c r="A20" s="24"/>
+      <c r="B20" s="24"/>
+      <c r="C20" s="24"/>
       <c r="D20" s="13"/>
       <c r="E20" s="13"/>
       <c r="F20" s="13"/>
@@ -2336,20 +2327,20 @@
       <c r="P20" s="13"/>
       <c r="Q20" s="13"/>
       <c r="R20" s="13"/>
-      <c r="S20" s="21"/>
-      <c r="T20" s="21"/>
-      <c r="U20" s="21"/>
+      <c r="S20" s="20"/>
+      <c r="T20" s="20"/>
+      <c r="U20" s="20"/>
       <c r="V20" s="13"/>
       <c r="W20" s="13"/>
       <c r="X20" s="13"/>
-      <c r="Y20" s="23"/>
-      <c r="Z20" s="6"/>
-      <c r="AA20" s="6"/>
+      <c r="Y20" s="22"/>
+      <c r="Z20" s="22"/>
+      <c r="AA20" s="22"/>
     </row>
     <row r="21" spans="1:27">
-      <c r="A21" s="13"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
+      <c r="A21" s="24"/>
+      <c r="B21" s="24"/>
+      <c r="C21" s="24"/>
       <c r="D21" s="13"/>
       <c r="E21" s="13"/>
       <c r="F21" s="13"/>
@@ -2365,20 +2356,20 @@
       <c r="P21" s="13"/>
       <c r="Q21" s="13"/>
       <c r="R21" s="13"/>
-      <c r="S21" s="21"/>
-      <c r="T21" s="21"/>
-      <c r="U21" s="21"/>
+      <c r="S21" s="20"/>
+      <c r="T21" s="20"/>
+      <c r="U21" s="20"/>
       <c r="V21" s="13"/>
       <c r="W21" s="13"/>
       <c r="X21" s="13"/>
-      <c r="Y21" s="23"/>
-      <c r="Z21" s="6"/>
-      <c r="AA21" s="6"/>
+      <c r="Y21" s="22"/>
+      <c r="Z21" s="22"/>
+      <c r="AA21" s="22"/>
     </row>
     <row r="22" spans="1:27">
-      <c r="A22" s="13"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
+      <c r="A22" s="24"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="24"/>
       <c r="D22" s="13"/>
       <c r="E22" s="13"/>
       <c r="F22" s="13"/>
@@ -2394,20 +2385,20 @@
       <c r="P22" s="13"/>
       <c r="Q22" s="13"/>
       <c r="R22" s="13"/>
-      <c r="S22" s="21"/>
-      <c r="T22" s="21"/>
-      <c r="U22" s="21"/>
+      <c r="S22" s="20"/>
+      <c r="T22" s="20"/>
+      <c r="U22" s="20"/>
       <c r="V22" s="13"/>
       <c r="W22" s="13"/>
       <c r="X22" s="13"/>
-      <c r="Y22" s="23"/>
-      <c r="Z22" s="6"/>
-      <c r="AA22" s="6"/>
+      <c r="Y22" s="22"/>
+      <c r="Z22" s="22"/>
+      <c r="AA22" s="22"/>
     </row>
     <row r="23" spans="1:27">
-      <c r="A23" s="13"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
+      <c r="A23" s="24"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="24"/>
       <c r="D23" s="13"/>
       <c r="E23" s="13"/>
       <c r="F23" s="13"/>
@@ -2423,20 +2414,20 @@
       <c r="P23" s="13"/>
       <c r="Q23" s="13"/>
       <c r="R23" s="13"/>
-      <c r="S23" s="21"/>
-      <c r="T23" s="21"/>
-      <c r="U23" s="21"/>
+      <c r="S23" s="20"/>
+      <c r="T23" s="20"/>
+      <c r="U23" s="20"/>
       <c r="V23" s="13"/>
       <c r="W23" s="13"/>
       <c r="X23" s="13"/>
-      <c r="Y23" s="23"/>
-      <c r="Z23" s="6"/>
-      <c r="AA23" s="6"/>
+      <c r="Y23" s="22"/>
+      <c r="Z23" s="22"/>
+      <c r="AA23" s="22"/>
     </row>
     <row r="24" spans="1:27">
-      <c r="A24" s="13"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
+      <c r="A24" s="24"/>
+      <c r="B24" s="24"/>
+      <c r="C24" s="24"/>
       <c r="D24" s="13"/>
       <c r="E24" s="13"/>
       <c r="F24" s="13"/>
@@ -2452,20 +2443,20 @@
       <c r="P24" s="13"/>
       <c r="Q24" s="13"/>
       <c r="R24" s="13"/>
-      <c r="S24" s="21"/>
-      <c r="T24" s="21"/>
-      <c r="U24" s="21"/>
+      <c r="S24" s="20"/>
+      <c r="T24" s="20"/>
+      <c r="U24" s="20"/>
       <c r="V24" s="13"/>
       <c r="W24" s="13"/>
       <c r="X24" s="13"/>
-      <c r="Y24" s="23"/>
-      <c r="Z24" s="6"/>
-      <c r="AA24" s="6"/>
+      <c r="Y24" s="22"/>
+      <c r="Z24" s="22"/>
+      <c r="AA24" s="22"/>
     </row>
     <row r="25" spans="1:27">
-      <c r="A25" s="13"/>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
+      <c r="A25" s="24"/>
+      <c r="B25" s="24"/>
+      <c r="C25" s="24"/>
       <c r="D25" s="13"/>
       <c r="E25" s="13"/>
       <c r="F25" s="13"/>
@@ -2481,20 +2472,20 @@
       <c r="P25" s="13"/>
       <c r="Q25" s="13"/>
       <c r="R25" s="13"/>
-      <c r="S25" s="21"/>
-      <c r="T25" s="21"/>
-      <c r="U25" s="21"/>
+      <c r="S25" s="20"/>
+      <c r="T25" s="20"/>
+      <c r="U25" s="20"/>
       <c r="V25" s="13"/>
       <c r="W25" s="13"/>
       <c r="X25" s="13"/>
-      <c r="Y25" s="23"/>
-      <c r="Z25" s="6"/>
-      <c r="AA25" s="6"/>
+      <c r="Y25" s="22"/>
+      <c r="Z25" s="22"/>
+      <c r="AA25" s="22"/>
     </row>
     <row r="26" spans="1:27">
-      <c r="A26" s="13"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
+      <c r="A26" s="24"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="24"/>
       <c r="D26" s="13"/>
       <c r="E26" s="13"/>
       <c r="F26" s="13"/>
@@ -2510,20 +2501,20 @@
       <c r="P26" s="13"/>
       <c r="Q26" s="13"/>
       <c r="R26" s="13"/>
-      <c r="S26" s="21"/>
-      <c r="T26" s="21"/>
-      <c r="U26" s="21"/>
+      <c r="S26" s="20"/>
+      <c r="T26" s="20"/>
+      <c r="U26" s="20"/>
       <c r="V26" s="13"/>
       <c r="W26" s="13"/>
       <c r="X26" s="13"/>
-      <c r="Y26" s="23"/>
-      <c r="Z26" s="6"/>
-      <c r="AA26" s="6"/>
+      <c r="Y26" s="22"/>
+      <c r="Z26" s="22"/>
+      <c r="AA26" s="22"/>
     </row>
     <row r="27" spans="1:27">
-      <c r="A27" s="13"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
+      <c r="A27" s="24"/>
+      <c r="B27" s="24"/>
+      <c r="C27" s="24"/>
       <c r="D27" s="13"/>
       <c r="E27" s="13"/>
       <c r="F27" s="13"/>
@@ -2539,20 +2530,20 @@
       <c r="P27" s="13"/>
       <c r="Q27" s="13"/>
       <c r="R27" s="13"/>
-      <c r="S27" s="21"/>
-      <c r="T27" s="21"/>
-      <c r="U27" s="21"/>
+      <c r="S27" s="20"/>
+      <c r="T27" s="20"/>
+      <c r="U27" s="20"/>
       <c r="V27" s="13"/>
       <c r="W27" s="13"/>
       <c r="X27" s="13"/>
-      <c r="Y27" s="23"/>
-      <c r="Z27" s="6"/>
-      <c r="AA27" s="6"/>
+      <c r="Y27" s="22"/>
+      <c r="Z27" s="22"/>
+      <c r="AA27" s="22"/>
     </row>
     <row r="28" spans="1:27">
-      <c r="A28" s="13"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
+      <c r="A28" s="24"/>
+      <c r="B28" s="24"/>
+      <c r="C28" s="24"/>
       <c r="D28" s="13"/>
       <c r="E28" s="13"/>
       <c r="F28" s="13"/>
@@ -2568,20 +2559,20 @@
       <c r="P28" s="13"/>
       <c r="Q28" s="13"/>
       <c r="R28" s="13"/>
-      <c r="S28" s="21"/>
-      <c r="T28" s="21"/>
-      <c r="U28" s="21"/>
+      <c r="S28" s="20"/>
+      <c r="T28" s="20"/>
+      <c r="U28" s="20"/>
       <c r="V28" s="13"/>
       <c r="W28" s="13"/>
       <c r="X28" s="13"/>
-      <c r="Y28" s="23"/>
-      <c r="Z28" s="6"/>
-      <c r="AA28" s="6"/>
+      <c r="Y28" s="22"/>
+      <c r="Z28" s="22"/>
+      <c r="AA28" s="22"/>
     </row>
     <row r="29" spans="1:27">
-      <c r="A29" s="13"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
+      <c r="A29" s="24"/>
+      <c r="B29" s="24"/>
+      <c r="C29" s="24"/>
       <c r="D29" s="13"/>
       <c r="E29" s="13"/>
       <c r="F29" s="13"/>
@@ -2597,20 +2588,20 @@
       <c r="P29" s="13"/>
       <c r="Q29" s="13"/>
       <c r="R29" s="13"/>
-      <c r="S29" s="21"/>
-      <c r="T29" s="21"/>
-      <c r="U29" s="21"/>
+      <c r="S29" s="20"/>
+      <c r="T29" s="20"/>
+      <c r="U29" s="20"/>
       <c r="V29" s="13"/>
       <c r="W29" s="13"/>
       <c r="X29" s="13"/>
-      <c r="Y29" s="23"/>
-      <c r="Z29" s="6"/>
-      <c r="AA29" s="6"/>
+      <c r="Y29" s="22"/>
+      <c r="Z29" s="22"/>
+      <c r="AA29" s="22"/>
     </row>
     <row r="30" spans="1:27">
-      <c r="A30" s="13"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
+      <c r="A30" s="24"/>
+      <c r="B30" s="24"/>
+      <c r="C30" s="24"/>
       <c r="D30" s="13"/>
       <c r="E30" s="13"/>
       <c r="F30" s="13"/>
@@ -2626,20 +2617,20 @@
       <c r="P30" s="13"/>
       <c r="Q30" s="13"/>
       <c r="R30" s="13"/>
-      <c r="S30" s="21"/>
-      <c r="T30" s="21"/>
-      <c r="U30" s="21"/>
+      <c r="S30" s="20"/>
+      <c r="T30" s="20"/>
+      <c r="U30" s="20"/>
       <c r="V30" s="13"/>
       <c r="W30" s="13"/>
       <c r="X30" s="13"/>
-      <c r="Y30" s="23"/>
-      <c r="Z30" s="6"/>
-      <c r="AA30" s="6"/>
+      <c r="Y30" s="22"/>
+      <c r="Z30" s="22"/>
+      <c r="AA30" s="22"/>
     </row>
     <row r="31" spans="1:27">
-      <c r="A31" s="13"/>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
+      <c r="A31" s="24"/>
+      <c r="B31" s="24"/>
+      <c r="C31" s="24"/>
       <c r="D31" s="13"/>
       <c r="E31" s="13"/>
       <c r="F31" s="13"/>
@@ -2655,20 +2646,20 @@
       <c r="P31" s="13"/>
       <c r="Q31" s="13"/>
       <c r="R31" s="13"/>
-      <c r="S31" s="21"/>
-      <c r="T31" s="21"/>
-      <c r="U31" s="21"/>
+      <c r="S31" s="20"/>
+      <c r="T31" s="20"/>
+      <c r="U31" s="20"/>
       <c r="V31" s="13"/>
       <c r="W31" s="13"/>
       <c r="X31" s="13"/>
-      <c r="Y31" s="23"/>
-      <c r="Z31" s="6"/>
-      <c r="AA31" s="6"/>
+      <c r="Y31" s="22"/>
+      <c r="Z31" s="22"/>
+      <c r="AA31" s="22"/>
     </row>
     <row r="32" spans="1:27">
-      <c r="A32" s="13"/>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
+      <c r="A32" s="24"/>
+      <c r="B32" s="24"/>
+      <c r="C32" s="24"/>
       <c r="D32" s="13"/>
       <c r="E32" s="13"/>
       <c r="F32" s="13"/>
@@ -2684,20 +2675,20 @@
       <c r="P32" s="13"/>
       <c r="Q32" s="13"/>
       <c r="R32" s="13"/>
-      <c r="S32" s="21"/>
-      <c r="T32" s="21"/>
-      <c r="U32" s="21"/>
+      <c r="S32" s="20"/>
+      <c r="T32" s="20"/>
+      <c r="U32" s="20"/>
       <c r="V32" s="13"/>
       <c r="W32" s="13"/>
       <c r="X32" s="13"/>
-      <c r="Y32" s="23"/>
-      <c r="Z32" s="6"/>
-      <c r="AA32" s="6"/>
+      <c r="Y32" s="22"/>
+      <c r="Z32" s="22"/>
+      <c r="AA32" s="22"/>
     </row>
     <row r="33" spans="1:27">
-      <c r="A33" s="13"/>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
+      <c r="A33" s="24"/>
+      <c r="B33" s="24"/>
+      <c r="C33" s="24"/>
       <c r="D33" s="13"/>
       <c r="E33" s="13"/>
       <c r="F33" s="13"/>
@@ -2713,20 +2704,20 @@
       <c r="P33" s="13"/>
       <c r="Q33" s="13"/>
       <c r="R33" s="13"/>
-      <c r="S33" s="21"/>
-      <c r="T33" s="21"/>
-      <c r="U33" s="21"/>
+      <c r="S33" s="20"/>
+      <c r="T33" s="20"/>
+      <c r="U33" s="20"/>
       <c r="V33" s="13"/>
       <c r="W33" s="13"/>
       <c r="X33" s="13"/>
-      <c r="Y33" s="23"/>
-      <c r="Z33" s="6"/>
-      <c r="AA33" s="6"/>
+      <c r="Y33" s="22"/>
+      <c r="Z33" s="22"/>
+      <c r="AA33" s="22"/>
     </row>
     <row r="34" spans="1:27">
-      <c r="A34" s="13"/>
-      <c r="B34" s="13"/>
-      <c r="C34" s="13"/>
+      <c r="A34" s="24"/>
+      <c r="B34" s="24"/>
+      <c r="C34" s="24"/>
       <c r="D34" s="13"/>
       <c r="E34" s="13"/>
       <c r="F34" s="13"/>
@@ -2742,40 +2733,25 @@
       <c r="P34" s="13"/>
       <c r="Q34" s="13"/>
       <c r="R34" s="13"/>
-      <c r="S34" s="21"/>
-      <c r="T34" s="21"/>
-      <c r="U34" s="21"/>
+      <c r="S34" s="20"/>
+      <c r="T34" s="20"/>
+      <c r="U34" s="20"/>
       <c r="V34" s="13"/>
       <c r="W34" s="13"/>
       <c r="X34" s="13"/>
-      <c r="Y34" s="23"/>
-      <c r="Z34" s="6"/>
-      <c r="AA34" s="6"/>
+      <c r="Y34" s="22"/>
+      <c r="Z34" s="22"/>
+      <c r="AA34" s="22"/>
     </row>
   </sheetData>
   <phoneticPr fontId="13" type="noConversion"/>
-  <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576">
-      <formula1>"01 是,02 否"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G1048576">
-      <formula1>"01 境内,02 境外"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1:I1048576">
-      <formula1>"26 其他非法人组织,25 合伙企业,24 个人独资企业,23 私募基金,22 社会保障类基金,21 保险资产管理计划,20 期货资产管理计划,19 基金资产管理计划,18 券商资产管理计划,17 信托产品,16 其他法人机构,15 机关,14 社会服务机构,13 基金会,12 社会团体,11 事业单位,10 其他金融机构,09 期货公司,08 保险公司,07 基金公司,06 证券公司,05 信托公司,04 银行,03 私人银行客户,02 高净值客户,01 普通个人"</formula1>
-    </dataValidation>
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J1:J1048576">
       <formula1>"00 居民身份证,01 临时居民身份证,02 户口簿,10 军官证,11 警官证,12 文职干部证,13 士兵证,14 军事院校学员证,15 离休干部荣誉证,16 军官退休证,17 文职干部退休证,20 中华人民共和国护照,21 外国护照,22 港澳往来内地通行证,23 台湾往来内地通行证,24 外国人永久居留证,99 其他,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q1:Q1048576">
-      <formula1>"01 男,02 女"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R1:R1048576">
-      <formula1>"01 保守型,02 稳健型,03 平衡型,04 成长型,05 进取型"</formula1>
-    </dataValidation>
   </dataValidations>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -2804,162 +2780,162 @@
     </row>
     <row r="2" spans="1:1" ht="38.25" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="33" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="33" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="3" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="4" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="4" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="4" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="4" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="4" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="4" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="4" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="4" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="4" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="4" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="4" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="4" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="4" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="4" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="4" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="4" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="4" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="4" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="4" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="4" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="4" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="4" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="4" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="4" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="4" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="4" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="4" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="4" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:1">
@@ -2967,1382 +2943,1382 @@
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="5" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="4" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="4" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="4" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="4" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="4" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="4" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="4" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="4" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="4" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="4" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="6" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="7" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="7" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="8" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="9" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="9" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="9" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="9" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="9" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="9" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="9" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="9" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="9" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="9" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="9" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" s="9" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="9" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" s="9" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="9" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="9" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="9" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="9" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" s="9" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="9" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="9" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="9" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="9" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" s="9" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="9" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="9" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="9" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" s="9" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="9" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" s="9" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" s="9" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" s="9" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="9" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" s="9" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" s="9" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" s="9" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" s="9" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" s="9" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" s="9" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112" s="9" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" s="9" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114" s="9" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115" s="9" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" s="9" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" s="9" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" s="9" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" s="9" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120" s="9" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" s="9" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
     </row>
     <row r="122" spans="1:1">
       <c r="A122" s="9" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" s="9" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" s="9" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" s="9" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
     </row>
     <row r="126" spans="1:1">
       <c r="A126" s="9" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
     </row>
     <row r="127" spans="1:1">
       <c r="A127" s="9" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" s="9" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="9" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" s="9" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" s="9" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
     </row>
     <row r="132" spans="1:1">
       <c r="A132" s="9" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
     </row>
     <row r="133" spans="1:1">
       <c r="A133" s="9" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
     </row>
     <row r="134" spans="1:1">
       <c r="A134" s="9" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135" s="9" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" s="9" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" s="9" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138" s="9" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" s="9" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
     </row>
     <row r="140" spans="1:1">
       <c r="A140" s="9" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" s="9" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142" s="9" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="143" spans="1:1">
       <c r="A143" s="9" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
     </row>
     <row r="144" spans="1:1">
       <c r="A144" s="9" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
     </row>
     <row r="145" spans="1:1">
       <c r="A145" s="9" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
     </row>
     <row r="146" spans="1:1">
       <c r="A146" s="9" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
     </row>
     <row r="147" spans="1:1">
       <c r="A147" s="9" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
     </row>
     <row r="148" spans="1:1">
       <c r="A148" s="9" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
     </row>
     <row r="149" spans="1:1">
       <c r="A149" s="9" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
     </row>
     <row r="150" spans="1:1">
       <c r="A150" s="9" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
     </row>
     <row r="151" spans="1:1">
       <c r="A151" s="9" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
     </row>
     <row r="152" spans="1:1">
       <c r="A152" s="9" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
     </row>
     <row r="153" spans="1:1">
       <c r="A153" s="9" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
     </row>
     <row r="154" spans="1:1">
       <c r="A154" s="9" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
     </row>
     <row r="155" spans="1:1">
       <c r="A155" s="9" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
     </row>
     <row r="156" spans="1:1">
       <c r="A156" s="9" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
     </row>
     <row r="157" spans="1:1">
       <c r="A157" s="9" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
     </row>
     <row r="158" spans="1:1">
       <c r="A158" s="9" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
     </row>
     <row r="159" spans="1:1">
       <c r="A159" s="9" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
     </row>
     <row r="160" spans="1:1">
       <c r="A160" s="9" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
     </row>
     <row r="161" spans="1:1">
       <c r="A161" s="9" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
     </row>
     <row r="162" spans="1:1">
       <c r="A162" s="9" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
     </row>
     <row r="163" spans="1:1">
       <c r="A163" s="9" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
     </row>
     <row r="164" spans="1:1">
       <c r="A164" s="9" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
     </row>
     <row r="165" spans="1:1">
       <c r="A165" s="9" t="s">
-        <v>183</v>
+        <v>163</v>
       </c>
     </row>
     <row r="166" spans="1:1">
       <c r="A166" s="9" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
     </row>
     <row r="167" spans="1:1">
       <c r="A167" s="9" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
     </row>
     <row r="168" spans="1:1">
       <c r="A168" s="9" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
     </row>
     <row r="169" spans="1:1">
       <c r="A169" s="9" t="s">
-        <v>187</v>
+        <v>167</v>
       </c>
     </row>
     <row r="170" spans="1:1">
       <c r="A170" s="9" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
     </row>
     <row r="171" spans="1:1">
       <c r="A171" s="9" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
     </row>
     <row r="172" spans="1:1">
       <c r="A172" s="9" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
     </row>
     <row r="173" spans="1:1">
       <c r="A173" s="9" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
     </row>
     <row r="174" spans="1:1">
       <c r="A174" s="9" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
     </row>
     <row r="175" spans="1:1">
       <c r="A175" s="9" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
     </row>
     <row r="176" spans="1:1">
       <c r="A176" s="9" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
     </row>
     <row r="177" spans="1:1">
       <c r="A177" s="9" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
     </row>
     <row r="178" spans="1:1">
       <c r="A178" s="9" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
     </row>
     <row r="179" spans="1:1">
       <c r="A179" s="9" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
     </row>
     <row r="180" spans="1:1">
       <c r="A180" s="9" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
     </row>
     <row r="181" spans="1:1">
       <c r="A181" s="9" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
     </row>
     <row r="182" spans="1:1">
       <c r="A182" s="9" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
     </row>
     <row r="183" spans="1:1">
       <c r="A183" s="9" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
     </row>
     <row r="184" spans="1:1">
       <c r="A184" s="9" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
     </row>
     <row r="185" spans="1:1">
       <c r="A185" s="9" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
     </row>
     <row r="186" spans="1:1">
       <c r="A186" s="9" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
     </row>
     <row r="187" spans="1:1">
       <c r="A187" s="9" t="s">
-        <v>205</v>
+        <v>185</v>
       </c>
     </row>
     <row r="188" spans="1:1">
       <c r="A188" s="9" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
     </row>
     <row r="189" spans="1:1">
       <c r="A189" s="9" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="190" spans="1:1">
       <c r="A190" s="9" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
     </row>
     <row r="191" spans="1:1">
       <c r="A191" s="9" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
     </row>
     <row r="192" spans="1:1">
       <c r="A192" s="9" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
     </row>
     <row r="193" spans="1:1">
       <c r="A193" s="9" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
     </row>
     <row r="194" spans="1:1">
       <c r="A194" s="9" t="s">
-        <v>212</v>
+        <v>192</v>
       </c>
     </row>
     <row r="195" spans="1:1">
       <c r="A195" s="9" t="s">
-        <v>213</v>
+        <v>193</v>
       </c>
     </row>
     <row r="196" spans="1:1">
       <c r="A196" s="9" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
     </row>
     <row r="197" spans="1:1">
       <c r="A197" s="9" t="s">
-        <v>215</v>
+        <v>195</v>
       </c>
     </row>
     <row r="198" spans="1:1">
       <c r="A198" s="9" t="s">
-        <v>216</v>
+        <v>196</v>
       </c>
     </row>
     <row r="199" spans="1:1">
       <c r="A199" s="9" t="s">
-        <v>217</v>
+        <v>197</v>
       </c>
     </row>
     <row r="200" spans="1:1">
       <c r="A200" s="9" t="s">
-        <v>218</v>
+        <v>198</v>
       </c>
     </row>
     <row r="201" spans="1:1">
       <c r="A201" s="9" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
     </row>
     <row r="202" spans="1:1">
       <c r="A202" s="9" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
     </row>
     <row r="203" spans="1:1">
       <c r="A203" s="9" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
     </row>
     <row r="204" spans="1:1">
       <c r="A204" s="9" t="s">
-        <v>222</v>
+        <v>202</v>
       </c>
     </row>
     <row r="205" spans="1:1">
       <c r="A205" s="9" t="s">
-        <v>223</v>
+        <v>203</v>
       </c>
     </row>
     <row r="206" spans="1:1">
       <c r="A206" s="9" t="s">
-        <v>224</v>
+        <v>204</v>
       </c>
     </row>
     <row r="207" spans="1:1">
       <c r="A207" s="9" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
     </row>
     <row r="208" spans="1:1">
       <c r="A208" s="9" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
     </row>
     <row r="209" spans="1:1">
       <c r="A209" s="9" t="s">
-        <v>227</v>
+        <v>207</v>
       </c>
     </row>
     <row r="210" spans="1:1">
       <c r="A210" s="9" t="s">
-        <v>228</v>
+        <v>208</v>
       </c>
     </row>
     <row r="211" spans="1:1">
       <c r="A211" s="9" t="s">
-        <v>229</v>
+        <v>209</v>
       </c>
     </row>
     <row r="212" spans="1:1">
       <c r="A212" s="9" t="s">
-        <v>230</v>
+        <v>210</v>
       </c>
     </row>
     <row r="213" spans="1:1">
       <c r="A213" s="9" t="s">
-        <v>231</v>
+        <v>211</v>
       </c>
     </row>
     <row r="214" spans="1:1">
       <c r="A214" s="9" t="s">
-        <v>232</v>
+        <v>212</v>
       </c>
     </row>
     <row r="215" spans="1:1">
       <c r="A215" s="9" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
     </row>
     <row r="216" spans="1:1">
       <c r="A216" s="9" t="s">
-        <v>234</v>
+        <v>214</v>
       </c>
     </row>
     <row r="217" spans="1:1">
       <c r="A217" s="9" t="s">
-        <v>235</v>
+        <v>215</v>
       </c>
     </row>
     <row r="218" spans="1:1">
       <c r="A218" s="9" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
     </row>
     <row r="219" spans="1:1">
       <c r="A219" s="9" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
     </row>
     <row r="220" spans="1:1">
       <c r="A220" s="9" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
     </row>
     <row r="221" spans="1:1">
       <c r="A221" s="9" t="s">
-        <v>239</v>
+        <v>219</v>
       </c>
     </row>
     <row r="222" spans="1:1">
       <c r="A222" s="9" t="s">
-        <v>240</v>
+        <v>220</v>
       </c>
     </row>
     <row r="223" spans="1:1">
       <c r="A223" s="9" t="s">
-        <v>241</v>
+        <v>221</v>
       </c>
     </row>
     <row r="224" spans="1:1">
       <c r="A224" s="9" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
     </row>
     <row r="225" spans="1:1">
       <c r="A225" s="9" t="s">
-        <v>243</v>
+        <v>223</v>
       </c>
     </row>
     <row r="226" spans="1:1">
       <c r="A226" s="9" t="s">
-        <v>244</v>
+        <v>224</v>
       </c>
     </row>
     <row r="227" spans="1:1">
       <c r="A227" s="9" t="s">
-        <v>245</v>
+        <v>225</v>
       </c>
     </row>
     <row r="228" spans="1:1">
       <c r="A228" s="9" t="s">
-        <v>246</v>
+        <v>226</v>
       </c>
     </row>
     <row r="229" spans="1:1">
       <c r="A229" s="9" t="s">
-        <v>247</v>
+        <v>227</v>
       </c>
     </row>
     <row r="230" spans="1:1">
       <c r="A230" s="9" t="s">
-        <v>248</v>
+        <v>228</v>
       </c>
     </row>
     <row r="231" spans="1:1">
       <c r="A231" s="9" t="s">
-        <v>249</v>
+        <v>229</v>
       </c>
     </row>
     <row r="232" spans="1:1">
       <c r="A232" s="9" t="s">
-        <v>250</v>
+        <v>230</v>
       </c>
     </row>
     <row r="233" spans="1:1">
       <c r="A233" s="9" t="s">
-        <v>251</v>
+        <v>231</v>
       </c>
     </row>
     <row r="234" spans="1:1">
       <c r="A234" s="9" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
     </row>
     <row r="235" spans="1:1">
       <c r="A235" s="9" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
     </row>
     <row r="236" spans="1:1">
       <c r="A236" s="9" t="s">
-        <v>254</v>
+        <v>234</v>
       </c>
     </row>
     <row r="237" spans="1:1">
       <c r="A237" s="9" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
     </row>
     <row r="238" spans="1:1">
       <c r="A238" s="9" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
     </row>
     <row r="239" spans="1:1">
       <c r="A239" s="9" t="s">
-        <v>257</v>
+        <v>237</v>
       </c>
     </row>
     <row r="240" spans="1:1">
       <c r="A240" s="9" t="s">
-        <v>258</v>
+        <v>238</v>
       </c>
     </row>
     <row r="241" spans="1:1">
       <c r="A241" s="9" t="s">
-        <v>259</v>
+        <v>239</v>
       </c>
     </row>
     <row r="242" spans="1:1">
       <c r="A242" s="9" t="s">
-        <v>260</v>
+        <v>240</v>
       </c>
     </row>
     <row r="243" spans="1:1">
       <c r="A243" s="9" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
     </row>
     <row r="244" spans="1:1">
       <c r="A244" s="9" t="s">
-        <v>262</v>
+        <v>242</v>
       </c>
     </row>
     <row r="245" spans="1:1">
       <c r="A245" s="9" t="s">
-        <v>263</v>
+        <v>243</v>
       </c>
     </row>
     <row r="246" spans="1:1">
       <c r="A246" s="9" t="s">
-        <v>264</v>
+        <v>244</v>
       </c>
     </row>
     <row r="247" spans="1:1">
       <c r="A247" s="9" t="s">
-        <v>265</v>
+        <v>245</v>
       </c>
     </row>
     <row r="248" spans="1:1">
       <c r="A248" s="9" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
     </row>
     <row r="249" spans="1:1">
       <c r="A249" s="9" t="s">
-        <v>267</v>
+        <v>247</v>
       </c>
     </row>
     <row r="250" spans="1:1">
       <c r="A250" s="9" t="s">
-        <v>268</v>
+        <v>248</v>
       </c>
     </row>
     <row r="251" spans="1:1">
       <c r="A251" s="9" t="s">
-        <v>269</v>
+        <v>249</v>
       </c>
     </row>
     <row r="252" spans="1:1">
       <c r="A252" s="9" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
     </row>
     <row r="253" spans="1:1">
       <c r="A253" s="9" t="s">
-        <v>271</v>
+        <v>251</v>
       </c>
     </row>
     <row r="254" spans="1:1">
       <c r="A254" s="9" t="s">
-        <v>272</v>
+        <v>252</v>
       </c>
     </row>
     <row r="255" spans="1:1">
       <c r="A255" s="9" t="s">
-        <v>273</v>
+        <v>253</v>
       </c>
     </row>
     <row r="256" spans="1:1">
       <c r="A256" s="9" t="s">
-        <v>274</v>
+        <v>254</v>
       </c>
     </row>
     <row r="257" spans="1:1">
       <c r="A257" s="9" t="s">
-        <v>275</v>
+        <v>255</v>
       </c>
     </row>
     <row r="258" spans="1:1">
       <c r="A258" s="9" t="s">
-        <v>276</v>
+        <v>256</v>
       </c>
     </row>
     <row r="259" spans="1:1">
       <c r="A259" s="9" t="s">
-        <v>277</v>
+        <v>257</v>
       </c>
     </row>
     <row r="260" spans="1:1">
       <c r="A260" s="9" t="s">
-        <v>278</v>
+        <v>258</v>
       </c>
     </row>
     <row r="261" spans="1:1">
       <c r="A261" s="9" t="s">
-        <v>279</v>
+        <v>259</v>
       </c>
     </row>
     <row r="262" spans="1:1">
       <c r="A262" s="9" t="s">
-        <v>280</v>
+        <v>260</v>
       </c>
     </row>
     <row r="263" spans="1:1">
       <c r="A263" s="9" t="s">
-        <v>281</v>
+        <v>261</v>
       </c>
     </row>
     <row r="264" spans="1:1">
       <c r="A264" s="9" t="s">
-        <v>282</v>
+        <v>262</v>
       </c>
     </row>
     <row r="265" spans="1:1">
       <c r="A265" s="9" t="s">
-        <v>283</v>
+        <v>263</v>
       </c>
     </row>
     <row r="266" spans="1:1">
       <c r="A266" s="9" t="s">
-        <v>284</v>
+        <v>264</v>
       </c>
     </row>
     <row r="267" spans="1:1">
       <c r="A267" s="9" t="s">
-        <v>285</v>
+        <v>265</v>
       </c>
     </row>
     <row r="268" spans="1:1">
       <c r="A268" s="9" t="s">
-        <v>286</v>
+        <v>266</v>
       </c>
     </row>
     <row r="269" spans="1:1">
       <c r="A269" s="9" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
     </row>
     <row r="270" spans="1:1">
       <c r="A270" s="9" t="s">
-        <v>288</v>
+        <v>268</v>
       </c>
     </row>
     <row r="271" spans="1:1">
       <c r="A271" s="9" t="s">
-        <v>289</v>
+        <v>269</v>
       </c>
     </row>
     <row r="272" spans="1:1">
       <c r="A272" s="9" t="s">
-        <v>290</v>
+        <v>270</v>
       </c>
     </row>
     <row r="273" spans="1:1">
       <c r="A273" s="9" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
     </row>
     <row r="274" spans="1:1">
       <c r="A274" s="9" t="s">
-        <v>292</v>
+        <v>272</v>
       </c>
     </row>
     <row r="275" spans="1:1">
       <c r="A275" s="9" t="s">
-        <v>293</v>
+        <v>273</v>
       </c>
     </row>
     <row r="276" spans="1:1">
       <c r="A276" s="9" t="s">
-        <v>294</v>
+        <v>274</v>
       </c>
     </row>
     <row r="277" spans="1:1">
       <c r="A277" s="9" t="s">
-        <v>295</v>
+        <v>275</v>
       </c>
     </row>
     <row r="278" spans="1:1">
       <c r="A278" s="9" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
     </row>
     <row r="279" spans="1:1">
       <c r="A279" s="9" t="s">
-        <v>297</v>
+        <v>277</v>
       </c>
     </row>
     <row r="280" spans="1:1">
       <c r="A280" s="9" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
     </row>
     <row r="281" spans="1:1">
       <c r="A281" s="9" t="s">
-        <v>299</v>
+        <v>279</v>
       </c>
     </row>
     <row r="282" spans="1:1">
       <c r="A282" s="9" t="s">
-        <v>300</v>
+        <v>280</v>
       </c>
     </row>
     <row r="283" spans="1:1">
       <c r="A283" s="9" t="s">
-        <v>301</v>
+        <v>281</v>
       </c>
     </row>
     <row r="284" spans="1:1">
       <c r="A284" s="9" t="s">
-        <v>302</v>
+        <v>282</v>
       </c>
     </row>
     <row r="285" spans="1:1">
       <c r="A285" s="9" t="s">
-        <v>303</v>
+        <v>283</v>
       </c>
     </row>
     <row r="286" spans="1:1">
       <c r="A286" s="9" t="s">
-        <v>304</v>
+        <v>284</v>
       </c>
     </row>
     <row r="287" spans="1:1">
       <c r="A287" s="9" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
     </row>
     <row r="288" spans="1:1">
       <c r="A288" s="9" t="s">
-        <v>306</v>
+        <v>286</v>
       </c>
     </row>
     <row r="289" spans="1:1">
       <c r="A289" s="9" t="s">
-        <v>307</v>
+        <v>287</v>
       </c>
     </row>
     <row r="290" spans="1:1">
       <c r="A290" s="9" t="s">
-        <v>308</v>
+        <v>288</v>
       </c>
     </row>
     <row r="291" spans="1:1">
       <c r="A291" s="9" t="s">
-        <v>309</v>
+        <v>289</v>
       </c>
     </row>
     <row r="292" spans="1:1">
       <c r="A292" s="9" t="s">
-        <v>310</v>
+        <v>290</v>
       </c>
     </row>
     <row r="293" spans="1:1">
       <c r="A293" s="9" t="s">
-        <v>311</v>
+        <v>291</v>
       </c>
     </row>
     <row r="294" spans="1:1">
       <c r="A294" s="9" t="s">
-        <v>312</v>
+        <v>292</v>
       </c>
     </row>
     <row r="295" spans="1:1">
       <c r="A295" s="9" t="s">
-        <v>313</v>
+        <v>293</v>
       </c>
     </row>
     <row r="296" spans="1:1">
       <c r="A296" s="9" t="s">
-        <v>314</v>
+        <v>294</v>
       </c>
     </row>
     <row r="297" spans="1:1">
       <c r="A297" s="9" t="s">
-        <v>315</v>
+        <v>295</v>
       </c>
     </row>
     <row r="298" spans="1:1">
       <c r="A298" s="9" t="s">
-        <v>316</v>
+        <v>296</v>
       </c>
     </row>
     <row r="299" spans="1:1">
       <c r="A299" s="9" t="s">
-        <v>317</v>
+        <v>297</v>
       </c>
     </row>
     <row r="300" spans="1:1">
       <c r="A300" s="9" t="s">
-        <v>318</v>
+        <v>298</v>
       </c>
     </row>
     <row r="301" spans="1:1">
       <c r="A301" s="9" t="s">
-        <v>319</v>
+        <v>299</v>
       </c>
     </row>
     <row r="302" spans="1:1">
       <c r="A302" s="9" t="s">
-        <v>320</v>
+        <v>300</v>
       </c>
     </row>
     <row r="303" spans="1:1">
       <c r="A303" s="9" t="s">
-        <v>321</v>
+        <v>301</v>
       </c>
     </row>
     <row r="304" spans="1:1">
       <c r="A304" s="9" t="s">
-        <v>322</v>
+        <v>302</v>
       </c>
     </row>
     <row r="305" spans="1:1">
       <c r="A305" s="9" t="s">
-        <v>323</v>
+        <v>303</v>
       </c>
     </row>
     <row r="306" spans="1:1">
       <c r="A306" s="9" t="s">
-        <v>324</v>
+        <v>304</v>
       </c>
     </row>
     <row r="307" spans="1:1">
       <c r="A307" s="9" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
     </row>
     <row r="308" spans="1:1">
       <c r="A308" s="9" t="s">
-        <v>326</v>
+        <v>306</v>
       </c>
     </row>
     <row r="309" spans="1:1">
       <c r="A309" s="9" t="s">
-        <v>327</v>
+        <v>307</v>
       </c>
     </row>
     <row r="310" spans="1:1">
       <c r="A310" s="9" t="s">
-        <v>328</v>
+        <v>308</v>
       </c>
     </row>
     <row r="311" spans="1:1">
       <c r="A311" s="9" t="s">
-        <v>329</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
